--- a/data/valuebets_database_2025-07-16.xlsx
+++ b/data/valuebets_database_2025-07-16.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>19/07 21:30</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>60</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45854.08086550765</v>
+        <v>45854.08086550926</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>19/07 19:30</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>60</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45854.08086550765</v>
+        <v>45854.08086550926</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>17/07 01:00</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>55</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45854.08086550765</v>
+        <v>45854.08086550926</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>19/07 21:45</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>55</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45854.08086550765</v>
+        <v>45854.08086550926</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>18/07 23:00</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>55</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45854.08086550765</v>
+        <v>45854.08086550926</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>20/07 19:45</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>55</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45854.08086550765</v>
+        <v>45854.08086550926</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>16/07 09:40</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
+      <c r="F8" t="n">
+        <v>2.25</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45854.08086550765</v>
+        <v>45854.08086550926</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>17/07 09:00</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
+      <c r="F9" t="n">
+        <v>2.1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45854.08086550765</v>
+        <v>45854.08086550926</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>16/07 23:00</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>50</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45854.08086550765</v>
+        <v>45854.08086550926</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>16/07 02:10</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
+      <c r="F11" t="n">
+        <v>1.45</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45854.08086550765</v>
+        <v>45854.08086550926</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>20/07 00:30</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>50</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45854.08086550765</v>
+        <v>45854.08086550926</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>16/07 09:00</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
+      <c r="F13" t="n">
+        <v>4.2</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45854.08086550765</v>
+        <v>45854.08086550926</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>20/07 09:00</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>55</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45854.08086550765</v>
+        <v>45854.08086550926</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>17/07 00:30</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>45</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45854.08086550765</v>
+        <v>45854.08086550926</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>16/07 23:30</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="F16" t="n">
+        <v>2.8</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45854.08086550765</v>
+        <v>45854.08086550926</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>21/07 00:00</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>50</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45854.08086550765</v>
+        <v>45854.08086550926</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>17/07 16:00</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>45</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45854.08086550765</v>
+        <v>45854.08086550926</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>25/07 22:00</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>40</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45854.08086550765</v>
+        <v>45854.08086550926</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>20/07 15:30</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>55</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45854.08086550765</v>
+        <v>45854.08086550926</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>17/07 00:30</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
+      <c r="F21" t="n">
+        <v>3.7</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45854.08086550765</v>
+        <v>45854.08086550926</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>19/07 01:10</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>45</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45854.08086550765</v>
+        <v>45854.08086550926</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>19/07 13:00</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>50</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45854.08086550765</v>
+        <v>45854.08086550926</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>21/07 18:30</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>45</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45854.08086550765</v>
+        <v>45854.08086550926</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>16/07 09:00</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>6.40</t>
-        </is>
+      <c r="F25" t="n">
+        <v>6.4</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45854.08086550765</v>
+        <v>45854.08086550926</v>
       </c>
     </row>
     <row r="26">
@@ -1585,10 +1537,8 @@
           <t>17/07 02:30</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F26" t="n">
+        <v>2.7</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1601,7 +1551,187 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45854.08086550765</v>
+        <v>45854.08086550926</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | Plus que 4.5 - break | Patrick Za</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Patrick Zahraj – Roman Andres BurruchagaATP - Gstaad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Plus que 4.5 - break</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>16/07 09:40</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>56,3%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+4,08%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45854.15194964935</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Philadelph</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Philadelphia Union – CF MontréalMLS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>16/07 23:30</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+1,49%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45854.15194964935</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 8.5 - tir cadré | Portland T</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Portland Timbers – Real Salt LakeÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Moins que 8.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>17/07 02:30</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>43,9%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+1,05%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45854.15194964935</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | San Diego </t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>San Diego FC – Toronto FCMLS</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>17/07 02:30</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+0,73%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45854.15194964935</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-16.xlsx
+++ b/data/valuebets_database_2025-07-16.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>16/07 09:40</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
+      <c r="F27" t="n">
+        <v>1.85</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45854.15194964935</v>
+        <v>45854.15194965278</v>
       </c>
     </row>
     <row r="28">
@@ -1625,10 +1623,8 @@
           <t>16/07 23:30</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F28" t="n">
+        <v>45</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1641,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45854.15194964935</v>
+        <v>45854.15194965278</v>
       </c>
     </row>
     <row r="29">
@@ -1670,10 +1666,8 @@
           <t>17/07 02:30</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
+      <c r="F29" t="n">
+        <v>2.3</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1686,7 +1680,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45854.15194964935</v>
+        <v>45854.15194965278</v>
       </c>
     </row>
     <row r="30">
@@ -1715,10 +1709,8 @@
           <t>17/07 02:30</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F30" t="n">
+        <v>45</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1731,7 +1723,142 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45854.15194964935</v>
+        <v>45854.15194965278</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball | X3e période[race to 15 regular time] | Phoenix Me</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Phoenix Mercury – Minnesota LynxUSA - WNBA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>X3e période[race to 15 regular time]</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>16/07 17:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>4,24%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+6,05%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45854.194529303</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 2 - aces | Hugo Gasto</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Hugo Gaston – Damir DzumhurATP - Bastad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>17/07 09:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>25,2%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+0,69%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45854.194529303</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Moins que 5 | Viktoria P</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Viktoria Plzen – Servette FCEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Moins que 5</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>22/07 17:00</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>93,5%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+0,06%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45854.194529303</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-16.xlsx
+++ b/data/valuebets_database_2025-07-16.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1752,10 +1752,8 @@
           <t>16/07 17:00</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>25.00</t>
-        </is>
+      <c r="F31" t="n">
+        <v>25</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1768,7 +1766,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45854.194529303</v>
+        <v>45854.19452930555</v>
       </c>
     </row>
     <row r="32">
@@ -1797,10 +1795,8 @@
           <t>17/07 09:00</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="F32" t="n">
+        <v>4</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1813,7 +1809,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45854.194529303</v>
+        <v>45854.19452930555</v>
       </c>
     </row>
     <row r="33">
@@ -1842,10 +1838,8 @@
           <t>22/07 17:00</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
+      <c r="F33" t="n">
+        <v>1.07</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1858,7 +1852,142 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45854.194529303</v>
+        <v>45854.19452930555</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Volleyball | H 1 (−2.5) | Iran – Pol</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Volleyball</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Iran – PologneInternational - Ligue des Nations</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>H 1 (−2.5)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>16/07 18:00</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>5,84%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+34,3%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45854.22795054653</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Water-polo | 1 | Croatie (F</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Water-polo</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Croatie (F) – Afr.Sud (F)Monde - Mondial 2025 F</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>17/07 02:35</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>54,4%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+6,17%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45854.22795054653</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 8.5 - tir cadré | New York R</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>New York Red Bulls – New England RevolutionÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Moins que 8.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>16/07 23:30</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>51,7%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+6,05%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45854.22795054653</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-16.xlsx
+++ b/data/valuebets_database_2025-07-16.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1881,10 +1881,8 @@
           <t>16/07 18:00</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>23.00</t>
-        </is>
+      <c r="F34" t="n">
+        <v>23</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1897,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45854.22795054653</v>
+        <v>45854.22795054398</v>
       </c>
     </row>
     <row r="35">
@@ -1926,10 +1924,8 @@
           <t>17/07 02:35</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
+      <c r="F35" t="n">
+        <v>1.95</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1942,7 +1938,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45854.22795054653</v>
+        <v>45854.22795054398</v>
       </c>
     </row>
     <row r="36">
@@ -1971,10 +1967,8 @@
           <t>16/07 23:30</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
+      <c r="F36" t="n">
+        <v>2.05</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1987,7 +1981,322 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45854.22795054653</v>
+        <v>45854.22795054398</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 28.5 - tirs | Botafogo –</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Botafogo – Vitoria BABrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Plus que 28.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>17/07 00:30</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>43,7%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+26,7%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45854.27470344823</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 9.5 - tir cadré | Alianza Li</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Alianza Lima – Gremio RSInternational - Copa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Plus que 9.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>17/07 00:30</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>33,0%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+22,0%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45854.27470344823</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 16.5 - tirs1re équipe | Bragantino</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Bragantino – Sao Paulo SPBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Plus que 16.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>17/07 00:30</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>44,2%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+19,4%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45854.27470344823</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Plus que 3.5 - tir cadré2e équipe | Palmeiras </t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Palmeiras – MirassolBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Plus que 3.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>16/07 22:00</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>35,8%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+14,4%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45854.27470344823</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Moins que 7.5 - tirs2e équipe | Bolivar – </t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Bolivar – PalestinoInternational - Copa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Moins que 7.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>16/07 22:00</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>39,6%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+4,96%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45854.27470344823</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Water-polo | Moins que 36.5 | Japon (F) </t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Water-polo</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Japon (F) – Gde-Bretagne (F)Monde - Mondial 2025 F</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Moins que 36.5</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>17/07 12:45</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>60,8%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+4,60%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45854.27470344823</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | X - aces | K.Majchrza</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>K.Majchrzak – I.BuseATP - Gstaad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>X - aces</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>16/07 08:30</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>12,8%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+2,60%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45854.27470344823</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-16.xlsx
+++ b/data/valuebets_database_2025-07-16.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2010,10 +2010,8 @@
           <t>17/07 00:30</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="F37" t="n">
+        <v>2.9</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2026,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45854.27470344823</v>
+        <v>45854.27470344907</v>
       </c>
     </row>
     <row r="38">
@@ -2055,10 +2053,8 @@
           <t>17/07 00:30</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
+      <c r="F38" t="n">
+        <v>3.7</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2071,7 +2067,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45854.27470344823</v>
+        <v>45854.27470344907</v>
       </c>
     </row>
     <row r="39">
@@ -2100,10 +2096,8 @@
           <t>17/07 00:30</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F39" t="n">
+        <v>2.7</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2116,7 +2110,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45854.27470344823</v>
+        <v>45854.27470344907</v>
       </c>
     </row>
     <row r="40">
@@ -2145,10 +2139,8 @@
           <t>16/07 22:00</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="F40" t="n">
+        <v>3.2</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2161,7 +2153,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45854.27470344823</v>
+        <v>45854.27470344907</v>
       </c>
     </row>
     <row r="41">
@@ -2190,10 +2182,8 @@
           <t>16/07 22:00</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2.65</t>
-        </is>
+      <c r="F41" t="n">
+        <v>2.65</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2206,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45854.27470344823</v>
+        <v>45854.27470344907</v>
       </c>
     </row>
     <row r="42">
@@ -2235,10 +2225,8 @@
           <t>17/07 12:45</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
+      <c r="F42" t="n">
+        <v>1.72</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2251,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45854.27470344823</v>
+        <v>45854.27470344907</v>
       </c>
     </row>
     <row r="43">
@@ -2280,10 +2268,8 @@
           <t>16/07 08:30</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
+      <c r="F43" t="n">
+        <v>8</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2296,7 +2282,232 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45854.27470344823</v>
+        <v>45854.27470344907</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | X - aces | M.Chwalins</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>M.Chwalinska – J.TeichmannWTA - Iasi</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>X - aces</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>16/07 07:30</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>30,7%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+22,9%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45854.30871365767</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 1 - aces | Juan Manue</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Juan Manuel Cerundolo – David GoffinATP - Gstaad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>16/07 15:30</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>64,0%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+15,3%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45854.30871365767</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 10.5 - tir cadré | Botafogo –</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Botafogo – Vitoria BABrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Plus que 10.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>17/07 00:30</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>34,1%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+12,5%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45854.30871365767</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 10.5 - tirs1re équipe | Norvège F.</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Norvège F. – Italie F.Europe - Euro Féminin 2025</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Moins que 10.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>16/07 19:00</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>47,0%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+11,9%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45854.30871365767</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 8.5 - tir cadré | Alianza Li</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Alianza Lima – Gremio RSInternational - Copa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Plus que 8.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>17/07 00:30</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>43,8%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+11,6%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45854.30871365767</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-16.xlsx
+++ b/data/valuebets_database_2025-07-16.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2311,10 +2311,8 @@
           <t>16/07 07:30</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="F44" t="n">
+        <v>4</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2327,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45854.30871365767</v>
+        <v>45854.30871365741</v>
       </c>
     </row>
     <row r="45">
@@ -2356,10 +2354,8 @@
           <t>16/07 15:30</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
+      <c r="F45" t="n">
+        <v>1.8</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2372,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45854.30871365767</v>
+        <v>45854.30871365741</v>
       </c>
     </row>
     <row r="46">
@@ -2401,10 +2397,8 @@
           <t>17/07 00:30</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="F46" t="n">
+        <v>3.3</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2417,7 +2411,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45854.30871365767</v>
+        <v>45854.30871365741</v>
       </c>
     </row>
     <row r="47">
@@ -2446,10 +2440,8 @@
           <t>16/07 19:00</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
+      <c r="F47" t="n">
+        <v>2.38</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2462,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45854.30871365767</v>
+        <v>45854.30871365741</v>
       </c>
     </row>
     <row r="48">
@@ -2491,10 +2483,8 @@
           <t>17/07 00:30</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
+      <c r="F48" t="n">
+        <v>2.55</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2507,7 +2497,187 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45854.30871365767</v>
+        <v>45854.30871365741</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 7.5 - tir cadré1re équipe | Botafogo –</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Botafogo – Vitoria BA385076e7 Brésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Plus que 7.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>17/07 00:30</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>29,3%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+5,64%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45854.35557951736</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | Moins que 4.5 - aces | Patrick Za</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Patrick Zahraj – Roman Andres BurruchagaATP - Gstaad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Moins que 4.5 - aces</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>16/07 09:40</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>47,4%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+4,35%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45854.35557951736</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | 1 - aces | K.Juvan – </t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>K.Juvan – L.ChiricoWTA - Hambourg F</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>16/07 10:30</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>66,7%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+3,36%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45854.35557951736</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 1 - aces | Andrea Pel</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Andrea Pellegrino – Tallon GriekspoorATP - Bastad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>16/07 10:55</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>12,8%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+2,19%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45854.35557951736</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-16.xlsx
+++ b/data/valuebets_database_2025-07-16.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2526,10 +2526,8 @@
           <t>17/07 00:30</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
+      <c r="F49" t="n">
+        <v>3.6</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2542,7 +2540,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45854.35557951736</v>
+        <v>45854.35557951389</v>
       </c>
     </row>
     <row r="50">
@@ -2571,10 +2569,8 @@
           <t>16/07 09:40</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
+      <c r="F50" t="n">
+        <v>2.2</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2587,7 +2583,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45854.35557951736</v>
+        <v>45854.35557951389</v>
       </c>
     </row>
     <row r="51">
@@ -2616,10 +2612,8 @@
           <t>16/07 10:30</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
+      <c r="F51" t="n">
+        <v>1.55</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2632,7 +2626,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45854.35557951736</v>
+        <v>45854.35557951389</v>
       </c>
     </row>
     <row r="52">
@@ -2661,10 +2655,8 @@
           <t>16/07 10:55</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
+      <c r="F52" t="n">
+        <v>8</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2677,7 +2669,142 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45854.35557951736</v>
+        <v>45854.35557951389</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 9.5 - tir cadré | Fluminense</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Fluminense – CruzeiroBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Plus que 9.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>17/07 22:30</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>40,1%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+28,5%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45854.3953970083</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Plus que 22.5 - tirs1re équipe | Bolivar – </t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Bolivar – PalestinoInternational - Copa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Plus que 22.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>16/07 22:00</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>34,5%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+3,42%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45854.3953970083</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 14.5 - tirs1re équipe | Bragantino</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Bragantino – Sao Paulo SPBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Plus que 14.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>17/07 00:30</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>60,4%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+2,67%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45854.3953970083</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-16.xlsx
+++ b/data/valuebets_database_2025-07-16.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2698,10 +2698,8 @@
           <t>17/07 22:30</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="F53" t="n">
+        <v>3.2</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2714,7 +2712,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45854.3953970083</v>
+        <v>45854.39539701389</v>
       </c>
     </row>
     <row r="54">
@@ -2743,10 +2741,8 @@
           <t>16/07 22:00</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F54" t="n">
+        <v>3</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2759,7 +2755,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45854.3953970083</v>
+        <v>45854.39539701389</v>
       </c>
     </row>
     <row r="55">
@@ -2788,10 +2784,8 @@
           <t>17/07 00:30</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
+      <c r="F55" t="n">
+        <v>1.7</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2804,7 +2798,97 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45854.3953970083</v>
+        <v>45854.39539701389</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis | 11-21er jeu | J Niemeier</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>J Niemeier – D YastremskaWTA Hamburg 2025</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>11-21er jeu</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>16/07 10:30</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>37,0%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+16,6%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45854.43540038575</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Alianza Li</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Alianza Lima – GremioCopa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>17/07 00:30</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+2,24%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45854.43540038575</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-16.xlsx
+++ b/data/valuebets_database_2025-07-16.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2827,10 +2827,8 @@
           <t>16/07 10:30</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
+      <c r="F56" t="n">
+        <v>3.15</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2843,7 +2841,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45854.43540038575</v>
+        <v>45854.43540038195</v>
       </c>
     </row>
     <row r="57">
@@ -2872,10 +2870,8 @@
           <t>17/07 00:30</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F57" t="n">
+        <v>40</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2888,7 +2884,187 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45854.43540038575</v>
+        <v>45854.43540038195</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 1 - aces | E.Ymer – L</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>E.Ymer – L.DarderiATP - Bastad H</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>16/07 13:35</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>49,3%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+6,05%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45854.47249257324</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 12.5 - tirs2e équipe | Norvège F.</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Norvège F. – Italie F.Europe - Euro Féminin 2025</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Moins que 12.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>16/07 19:00</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>39,6%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+4,12%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45854.47249257324</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | CA Tigre –</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>CA Tigre – Argentinos JuniorsLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>20/07 19:45</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+1,49%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45854.47249257324</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | 2 - aces | S.Cirstea </t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>S.Cirstea – V.GrachevaWTA - Iasi</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>16/07 15:30</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>20,3%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+1,36%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45854.47249257324</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-16.xlsx
+++ b/data/valuebets_database_2025-07-16.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2913,10 +2913,8 @@
           <t>16/07 13:35</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
+      <c r="F58" t="n">
+        <v>2.15</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2929,7 +2927,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45854.47249257324</v>
+        <v>45854.47249256945</v>
       </c>
     </row>
     <row r="59">
@@ -2958,10 +2956,8 @@
           <t>16/07 19:00</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
+      <c r="F59" t="n">
+        <v>2.63</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2974,7 +2970,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45854.47249257324</v>
+        <v>45854.47249256945</v>
       </c>
     </row>
     <row r="60">
@@ -3003,10 +2999,8 @@
           <t>20/07 19:45</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F60" t="n">
+        <v>45</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3019,7 +3013,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45854.47249257324</v>
+        <v>45854.47249256945</v>
       </c>
     </row>
     <row r="61">
@@ -3048,10 +3042,8 @@
           <t>16/07 15:30</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="F61" t="n">
+        <v>5</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3064,7 +3056,187 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45854.47249257324</v>
+        <v>45854.47249256945</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Red Bull B</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Red Bull Bragantino – Sao PauloSérie A</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>17/07 00:30</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+21,6%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45854.53475887571</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Dinamo Min</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Dinamo Minsk – LudogoretsLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>16/07 18:45</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+13,4%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45854.53475887571</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 7.5 - tir cadré | Portland T</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Portland Timbers – Real Salt LakeÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Moins que 7.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>17/07 02:30</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>32,1%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+5,87%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45854.53475887571</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Plus que 19.5 - tirs1re équipe | Bolivar – </t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Bolivar – PalestinoInternational - Copa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Plus que 19.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>16/07 22:00</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>56,4%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+4,30%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45854.53475887571</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-16.xlsx
+++ b/data/valuebets_database_2025-07-16.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3085,10 +3085,8 @@
           <t>17/07 00:30</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F62" t="n">
+        <v>55</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3101,7 +3099,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45854.53475887571</v>
+        <v>45854.53475887731</v>
       </c>
     </row>
     <row r="63">
@@ -3130,10 +3128,8 @@
           <t>16/07 18:45</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F63" t="n">
+        <v>50</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3146,7 +3142,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45854.53475887571</v>
+        <v>45854.53475887731</v>
       </c>
     </row>
     <row r="64">
@@ -3175,10 +3171,8 @@
           <t>17/07 02:30</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="F64" t="n">
+        <v>3.3</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3191,7 +3185,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45854.53475887571</v>
+        <v>45854.53475887731</v>
       </c>
     </row>
     <row r="65">
@@ -3220,10 +3214,8 @@
           <t>16/07 22:00</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
+      <c r="F65" t="n">
+        <v>1.85</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3236,7 +3228,142 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45854.53475887571</v>
+        <v>45854.53475887731</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Cukaricki </t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Cukaricki – FK NapredakSuperLiga</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>19/07 18:00</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+7,00%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45854.56913104938</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | Pas de buts | Étoile Rou</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Étoile Rouge Belgrade – Javor IvanjicaSerbie. Serbie - Super Liga</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>19/07 18:00</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>+5,61%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>45854.56913104938</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 9.5 - tir cadré | San Jose E</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>San Jose Earthquakes – FC DallasÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Moins que 9.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>17/07 02:30</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>43,9%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>+5,37%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>45854.56913104938</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-16.xlsx
+++ b/data/valuebets_database_2025-07-16.xlsx
@@ -3257,10 +3257,8 @@
           <t>19/07 18:00</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F66" t="n">
+        <v>40</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3273,7 +3271,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45854.56913104938</v>
+        <v>45854.56913105324</v>
       </c>
     </row>
     <row r="67">
@@ -3302,10 +3300,8 @@
           <t>19/07 18:00</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F67" t="n">
+        <v>45</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3318,7 +3314,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>45854.56913104938</v>
+        <v>45854.56913105324</v>
       </c>
     </row>
     <row r="68">
@@ -3347,10 +3343,8 @@
           <t>17/07 02:30</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
+      <c r="F68" t="n">
+        <v>2.4</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3363,7 +3357,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>45854.56913104938</v>
+        <v>45854.56913105324</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-16.xlsx
+++ b/data/valuebets_database_2025-07-16.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3360,6 +3360,51 @@
         <v>45854.56913105324</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Atlético B</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga – Atletico MineiroCopa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>18/07 00:30</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>+9,25%</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>45854.643604367</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-07-16.xlsx
+++ b/data/valuebets_database_2025-07-16.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3386,10 +3386,8 @@
           <t>18/07 00:30</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F69" t="n">
+        <v>45</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3402,7 +3400,52 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>45854.643604367</v>
+        <v>45854.64360436342</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 9.5 - tirs2e équipe | Linfield –</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Linfield – Shelbourne FCEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Moins que 9.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>16/07 18:45</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>34,6%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>+3,23%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>45854.68798825406</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-16.xlsx
+++ b/data/valuebets_database_2025-07-16.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3429,10 +3429,8 @@
           <t>16/07 18:45</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2.98</t>
-        </is>
+      <c r="F70" t="n">
+        <v>2.98</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3445,7 +3443,187 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>45854.68798825406</v>
+        <v>45854.68798825231</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 3.5 - tir cadré2e équipe | Alianza Li</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Alianza Lima – Gremio RSInternational - Copa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Plus que 3.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>17/07 00:30</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>54,6%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>+6,55%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>45854.72446346087</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 10.5 - tirs1re équipe | Ceara CE –</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ceara CE – CorinthiansBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Moins que 10.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>16/07 22:30</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>38,5%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>+5,86%</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>45854.72446346087</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | Plus que 1.5 - break1er participant | Govind Nan</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Govind Nanda – Denis ShapovalovATP - Los Cabos</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Plus que 1.5 - break1er participant</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>17/07 01:00</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>49,5%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>+3,87%</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>45854.72446346087</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 2 - aces | Adam Walto</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Adam Walton – Nishesh BasavareddyATP - Los Cabos</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>17/07 03:20</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>36,3%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>+3,35%</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>45854.72446346087</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-16.xlsx
+++ b/data/valuebets_database_2025-07-16.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3472,10 +3472,8 @@
           <t>17/07 00:30</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
+      <c r="F71" t="n">
+        <v>1.95</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3488,7 +3486,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>45854.72446346087</v>
+        <v>45854.72446346065</v>
       </c>
     </row>
     <row r="72">
@@ -3517,10 +3515,8 @@
           <t>16/07 22:30</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F72" t="n">
+        <v>2.75</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3533,7 +3529,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>45854.72446346087</v>
+        <v>45854.72446346065</v>
       </c>
     </row>
     <row r="73">
@@ -3562,10 +3558,8 @@
           <t>17/07 01:00</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
+      <c r="F73" t="n">
+        <v>2.1</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3578,7 +3572,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>45854.72446346087</v>
+        <v>45854.72446346065</v>
       </c>
     </row>
     <row r="74">
@@ -3607,10 +3601,8 @@
           <t>17/07 03:20</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
+      <c r="F74" t="n">
+        <v>2.85</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3623,7 +3615,97 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45854.72446346087</v>
+        <v>45854.72446346065</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 1 - aces | Camilo Ugo</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Camilo Ugo Carabelli – Botic Van De ZandschulpATP - Bastad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>17/07 09:00</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>29,7%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>+33,8%</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>45854.77363704849</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Atletico T</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Atletico Tucuman – Central CordobaLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>19/07 00:30</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>+8,77%</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>45854.77363704849</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-16.xlsx
+++ b/data/valuebets_database_2025-07-16.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I76"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3644,10 +3644,8 @@
           <t>17/07 09:00</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="F75" t="n">
+        <v>4.5</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3660,7 +3658,7 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>45854.77363704849</v>
+        <v>45854.77363704861</v>
       </c>
     </row>
     <row r="76">
@@ -3689,23 +3687,156 @@
           <t>19/07 00:30</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F76" t="n">
+        <v>45</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>+8,77%</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>45854.77363704861</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Tatran Pre</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Tatran Presov – Slovan BratislavaFortuna Liga</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>26/07 18:30</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
         <is>
           <t>45.00</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>+8,77%</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="n">
-        <v>45854.77363704849</v>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>+21,7%</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>45854.80516149458</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 12.5 - tirs1re équipe | Los Angele</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Los Angeles Galaxy – Austin FCÉtats-Unis - États-Unis MLS A9ZJ2X7R 385076e7</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Moins que 12.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>17/07 02:30</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>40,0%</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>+10,1%</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>45854.80516149458</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 13.5 - tirs1re équipe | FC Cincinn</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>FC Cincinnati – Inter Miami CFÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Plus que 13.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>16/07 23:30</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>54,3%</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>+5,40%</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>45854.80516149458</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-16.xlsx
+++ b/data/valuebets_database_2025-07-16.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3730,10 +3730,8 @@
           <t>26/07 18:30</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F77" t="n">
+        <v>45</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3746,7 +3744,7 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>45854.80516149458</v>
+        <v>45854.80516149306</v>
       </c>
     </row>
     <row r="78">
@@ -3775,10 +3773,8 @@
           <t>17/07 02:30</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F78" t="n">
+        <v>2.75</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3791,7 +3787,7 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>45854.80516149458</v>
+        <v>45854.80516149306</v>
       </c>
     </row>
     <row r="79">
@@ -3820,10 +3816,8 @@
           <t>16/07 23:30</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
+      <c r="F79" t="n">
+        <v>1.94</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3836,7 +3830,97 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>45854.80516149458</v>
+        <v>45854.80516149306</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 23.5 - tirs | Philadelph</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Philadelphia Union – CF MontréalÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Plus que 23.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>16/07 23:30</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>59,3%</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>+5,48%</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>45854.85160694638</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 7.5 - tir cadré | New York R</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>New York Red Bulls – New England RevolutionÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Plus que 7.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>16/07 23:30</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>61,8%</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>+4,38%</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>45854.85160694638</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-16.xlsx
+++ b/data/valuebets_database_2025-07-16.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:I83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3859,10 +3859,8 @@
           <t>16/07 23:30</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>1.78</t>
-        </is>
+      <c r="F80" t="n">
+        <v>1.78</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3875,7 +3873,7 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>45854.85160694638</v>
+        <v>45854.85160694444</v>
       </c>
     </row>
     <row r="81">
@@ -3904,10 +3902,8 @@
           <t>16/07 23:30</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
+      <c r="F81" t="n">
+        <v>1.69</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3920,7 +3916,97 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>45854.85160694638</v>
+        <v>45854.85160694444</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | BK Hacken </t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>BK Hacken – Spartak TrnavaLigue Europa</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>17/07 17:00</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>+9,38%</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>45854.89090596624</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 2 - aces | U.Carabell</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>U.Carabelli – Van De ZandschATP - Bastad H</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>17/07 09:00</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>65,2%</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>+7,63%</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>45854.89090596624</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-16.xlsx
+++ b/data/valuebets_database_2025-07-16.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3945,10 +3945,8 @@
           <t>17/07 17:00</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F82" t="n">
+        <v>45</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3961,7 +3959,7 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>45854.89090596624</v>
+        <v>45854.89090596064</v>
       </c>
     </row>
     <row r="83">
@@ -3990,10 +3988,8 @@
           <t>17/07 09:00</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
+      <c r="F83" t="n">
+        <v>1.65</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -4006,7 +4002,142 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>45854.89090596624</v>
+        <v>45854.89090596064</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Slavia Pra</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Slavia Prague – FC Hradec KraloveSynot League</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>20/07 18:00</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>+24,4%</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>45854.93247403323</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Velez Sars</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Velez Sarsfield – Instituto AC CordobaLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>26/07 22:00</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>+15,3%</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>45854.93247403323</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 13.5 - tirs1re équipe | Ceara CE –</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ceara CE – CorinthiansBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Plus que 13.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>16/07 22:30</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>36,9%</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>+6,88%</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>45854.93247403323</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-16.xlsx
+++ b/data/valuebets_database_2025-07-16.xlsx
@@ -4031,10 +4031,8 @@
           <t>20/07 18:00</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F84" t="n">
+        <v>55</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -4047,7 +4045,7 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>45854.93247403323</v>
+        <v>45854.93247402778</v>
       </c>
     </row>
     <row r="85">
@@ -4076,10 +4074,8 @@
           <t>26/07 22:00</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F85" t="n">
+        <v>50</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -4092,7 +4088,7 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>45854.93247403323</v>
+        <v>45854.93247402778</v>
       </c>
     </row>
     <row r="86">
@@ -4121,10 +4117,8 @@
           <t>16/07 22:30</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="F86" t="n">
+        <v>2.9</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -4137,7 +4131,7 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>45854.93247403323</v>
+        <v>45854.93247402778</v>
       </c>
     </row>
   </sheetData>
